--- a/AAII_Financials/Quarterly/MGRX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MGRX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="92">
   <si>
     <t>MGRX</t>
   </si>
@@ -656,93 +656,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -752,8 +753,11 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -767,11 +771,11 @@
         <v>100</v>
       </c>
       <c r="G8" s="3">
+        <v>100</v>
+      </c>
+      <c r="H8" s="3">
         <v>200</v>
       </c>
-      <c r="H8" s="3">
-        <v>100</v>
-      </c>
       <c r="I8" s="3">
         <v>100</v>
       </c>
@@ -779,7 +783,7 @@
         <v>100</v>
       </c>
       <c r="K8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L8" s="3">
         <v>200</v>
@@ -791,19 +795,19 @@
         <v>200</v>
       </c>
       <c r="O8" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P8" s="3">
         <v>100</v>
       </c>
       <c r="Q8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R8" s="3">
         <v>0</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
+      <c r="S8" s="3">
+        <v>0</v>
       </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
@@ -817,8 +821,11 @@
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -832,16 +839,16 @@
         <v>0</v>
       </c>
       <c r="G9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I9" s="3">
         <v>0</v>
       </c>
       <c r="J9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3">
         <v>100</v>
@@ -859,13 +866,13 @@
         <v>100</v>
       </c>
       <c r="P9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q9" s="3">
         <v>0</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
+      <c r="R9" s="3">
+        <v>0</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
@@ -882,8 +889,11 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -894,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G10" s="3">
         <v>100</v>
@@ -927,10 +937,10 @@
         <v>100</v>
       </c>
       <c r="Q10" s="3">
-        <v>0</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="R10" s="3">
+        <v>0</v>
       </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
@@ -947,8 +957,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -972,8 +985,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1004,20 +1018,20 @@
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3">
         <v>-400</v>
       </c>
-      <c r="N12" s="3">
-        <v>100</v>
-      </c>
       <c r="O12" s="3">
         <v>100</v>
       </c>
       <c r="P12" s="3">
         <v>100</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
+      <c r="Q12" s="3">
+        <v>100</v>
       </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
@@ -1037,8 +1051,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1102,25 +1119,28 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>1300</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
-        <v>100</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
+        <v>100</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
@@ -1146,8 +1166,8 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1167,8 +1187,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1176,23 +1199,23 @@
         <v>300</v>
       </c>
       <c r="E15" s="3">
+        <v>300</v>
+      </c>
+      <c r="F15" s="3">
         <v>1100</v>
       </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
       <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
         <v>800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>700</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
@@ -1232,8 +1255,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1254,62 +1280,63 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E17" s="3">
         <v>3200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>300</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1319,59 +1346,62 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-7500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-5200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2100</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-2200</v>
       </c>
       <c r="M18" s="3">
         <v>-2200</v>
       </c>
       <c r="N18" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="O18" s="3">
         <v>-1500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1000</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1384,8 +1414,11 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1409,13 +1442,14 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1424,43 +1458,43 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>100</v>
+      </c>
+      <c r="I20" s="3">
         <v>1400</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M20" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="N20" s="3">
         <v>300</v>
       </c>
       <c r="O20" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="P20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q20" s="3">
         <v>600</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
+      <c r="S20" s="3">
+        <v>0</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
@@ -1474,53 +1508,56 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-7500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-4400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-4100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1539,8 +1576,11 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1548,28 +1588,28 @@
         <v>300</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
         <v>300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>-500</v>
-      </c>
-      <c r="J22" s="3">
-        <v>200</v>
       </c>
       <c r="K22" s="3">
         <v>200</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
+      <c r="L22" s="3">
+        <v>200</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
@@ -1577,8 +1617,8 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1592,8 +1632,8 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
+      <c r="T22" s="3">
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
@@ -1604,62 +1644,65 @@
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-7600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-4800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2000</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-2400</v>
       </c>
       <c r="L23" s="3">
         <v>-2400</v>
       </c>
       <c r="M23" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="N23" s="3">
         <v>-2600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-300</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1669,8 +1712,11 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1713,8 +1759,8 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -1734,8 +1780,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1799,62 +1848,65 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-7600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-5400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2000</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-2400</v>
       </c>
       <c r="L26" s="3">
         <v>-2400</v>
       </c>
       <c r="M26" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="N26" s="3">
         <v>-2600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-300</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1864,62 +1916,65 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-7900</v>
       </c>
-      <c r="G27" s="3">
-        <v>-5400</v>
-      </c>
       <c r="H27" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="I27" s="3">
         <v>-5100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2300</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-2400</v>
       </c>
       <c r="L27" s="3">
         <v>-2400</v>
       </c>
       <c r="M27" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="N27" s="3">
         <v>-2600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-300</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1929,8 +1984,11 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1994,8 +2052,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2059,8 +2120,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2124,8 +2188,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2189,13 +2256,16 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -2204,43 +2274,43 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1400</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-300</v>
       </c>
       <c r="N32" s="3">
         <v>-300</v>
       </c>
       <c r="O32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-600</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
+      <c r="S32" s="3">
+        <v>0</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
@@ -2254,62 +2324,65 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-7600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-5400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2000</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-2400</v>
       </c>
       <c r="L33" s="3">
         <v>-2400</v>
       </c>
       <c r="M33" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="N33" s="3">
         <v>-2600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-300</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2319,8 +2392,11 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2384,62 +2460,65 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-7600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-5400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2000</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-2400</v>
       </c>
       <c r="L35" s="3">
         <v>-2400</v>
       </c>
       <c r="M35" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="N35" s="3">
         <v>-2600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-300</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2449,67 +2528,70 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2519,8 +2601,11 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2544,8 +2629,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2569,8 +2655,9 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2578,14 +2665,14 @@
         <v>200</v>
       </c>
       <c r="E41" s="3">
+        <v>200</v>
+      </c>
+      <c r="F41" s="3">
         <v>1500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>500</v>
       </c>
-      <c r="G41" s="3">
-        <v>100</v>
-      </c>
       <c r="H41" s="3">
         <v>100</v>
       </c>
@@ -2596,34 +2683,34 @@
         <v>100</v>
       </c>
       <c r="K41" s="3">
+        <v>100</v>
+      </c>
+      <c r="L41" s="3">
         <v>500</v>
       </c>
-      <c r="L41" s="3">
-        <v>0</v>
-      </c>
       <c r="M41" s="3">
+        <v>0</v>
+      </c>
+      <c r="N41" s="3">
         <v>700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>900</v>
       </c>
-      <c r="S41" s="3">
-        <v>0</v>
-      </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
+      <c r="T41" s="3">
+        <v>0</v>
       </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
@@ -2634,8 +2721,11 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2699,8 +2789,11 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2743,8 +2836,8 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -2764,8 +2857,11 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2787,8 +2883,8 @@
       <c r="I44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2805,8 +2901,8 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
+      <c r="P44" s="3">
+        <v>0</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
@@ -2823,14 +2919,17 @@
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V44" s="3">
-        <v>0</v>
+      <c r="V44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2838,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="E45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G45" s="3">
         <v>0</v>
@@ -2858,20 +2957,20 @@
       <c r="K45" s="3">
         <v>0</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3">
-        <v>100</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O45" s="3">
-        <v>100</v>
+      <c r="L45" s="3">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
+        <v>100</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q45" s="3">
         <v>0</v>
@@ -2879,8 +2978,8 @@
       <c r="R45" s="3">
         <v>0</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
+      <c r="S45" s="3">
+        <v>0</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
@@ -2894,8 +2993,11 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2903,52 +3005,52 @@
         <v>200</v>
       </c>
       <c r="E46" s="3">
+        <v>200</v>
+      </c>
+      <c r="F46" s="3">
         <v>1500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>600</v>
       </c>
-      <c r="G46" s="3">
-        <v>100</v>
-      </c>
       <c r="H46" s="3">
+        <v>100</v>
+      </c>
+      <c r="I46" s="3">
         <v>200</v>
       </c>
-      <c r="I46" s="3">
-        <v>100</v>
-      </c>
       <c r="J46" s="3">
         <v>100</v>
       </c>
       <c r="K46" s="3">
+        <v>100</v>
+      </c>
+      <c r="L46" s="3">
         <v>500</v>
       </c>
-      <c r="L46" s="3">
-        <v>100</v>
-      </c>
       <c r="M46" s="3">
+        <v>100</v>
+      </c>
+      <c r="N46" s="3">
         <v>800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>900</v>
       </c>
-      <c r="S46" s="3">
-        <v>0</v>
-      </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
+      <c r="T46" s="3">
+        <v>0</v>
       </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
@@ -2959,8 +3061,11 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3003,8 +3108,8 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3024,8 +3129,11 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3036,13 +3144,13 @@
         <v>300</v>
       </c>
       <c r="F48" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G48" s="3">
         <v>0</v>
       </c>
       <c r="H48" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3">
         <v>200</v>
@@ -3063,7 +3171,7 @@
         <v>200</v>
       </c>
       <c r="O48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="P48" s="3">
         <v>300</v>
@@ -3072,10 +3180,10 @@
         <v>300</v>
       </c>
       <c r="R48" s="3">
-        <v>0</v>
-      </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
+        <v>300</v>
+      </c>
+      <c r="S48" s="3">
+        <v>0</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
@@ -3089,37 +3197,40 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E49" s="3">
         <v>13900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>15900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>20700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>21500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>15200</v>
-      </c>
-      <c r="J49" s="3">
-        <v>14600</v>
       </c>
       <c r="K49" s="3">
         <v>14600</v>
       </c>
       <c r="L49" s="3">
-        <v>0</v>
+        <v>14600</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -3133,11 +3244,11 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
@@ -3154,8 +3265,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3219,8 +3333,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3284,8 +3401,11 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3313,14 +3433,14 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O52" s="3">
         <v>0</v>
@@ -3334,8 +3454,8 @@
       <c r="R52" s="3">
         <v>0</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
+      <c r="S52" s="3">
+        <v>0</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
@@ -3349,8 +3469,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3414,61 +3537,64 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E54" s="3">
         <v>14400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>16100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>16500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>20800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>21800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>15400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>15200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>900</v>
       </c>
-      <c r="S54" s="3">
-        <v>0</v>
-      </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
+      <c r="T54" s="3">
+        <v>0</v>
       </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
@@ -3479,8 +3605,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3504,8 +3633,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3529,41 +3659,42 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>900</v>
+      </c>
+      <c r="E57" s="3">
         <v>500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1200</v>
-      </c>
-      <c r="I57" s="3">
-        <v>800</v>
       </c>
       <c r="J57" s="3">
         <v>800</v>
       </c>
       <c r="K57" s="3">
+        <v>800</v>
+      </c>
+      <c r="L57" s="3">
         <v>700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1100</v>
       </c>
-      <c r="M57" s="3">
-        <v>100</v>
-      </c>
       <c r="N57" s="3">
         <v>100</v>
       </c>
@@ -3571,19 +3702,19 @@
         <v>100</v>
       </c>
       <c r="P57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q57" s="3">
         <v>0</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S57" s="3">
-        <v>0</v>
-      </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T57" s="3">
+        <v>0</v>
       </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
@@ -3594,41 +3725,44 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>100</v>
+      </c>
+      <c r="F58" s="3">
         <v>300</v>
       </c>
-      <c r="F58" s="3">
-        <v>100</v>
-      </c>
       <c r="G58" s="3">
+        <v>100</v>
+      </c>
+      <c r="H58" s="3">
         <v>600</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>200</v>
-      </c>
-      <c r="J58" s="3">
-        <v>300</v>
       </c>
       <c r="K58" s="3">
         <v>300</v>
       </c>
       <c r="L58" s="3">
+        <v>300</v>
+      </c>
+      <c r="M58" s="3">
         <v>200</v>
       </c>
-      <c r="M58" s="3">
-        <v>100</v>
-      </c>
       <c r="N58" s="3">
         <v>100</v>
       </c>
@@ -3639,16 +3773,16 @@
         <v>100</v>
       </c>
       <c r="Q58" s="3">
+        <v>100</v>
+      </c>
+      <c r="R58" s="3">
         <v>200</v>
       </c>
-      <c r="R58" s="3">
-        <v>100</v>
-      </c>
       <c r="S58" s="3">
         <v>100</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
+      <c r="T58" s="3">
+        <v>100</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
@@ -3659,16 +3793,19 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E59" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F59" s="3">
         <v>200</v>
@@ -3677,10 +3814,10 @@
         <v>200</v>
       </c>
       <c r="H59" s="3">
+        <v>200</v>
+      </c>
+      <c r="I59" s="3">
         <v>300</v>
-      </c>
-      <c r="I59" s="3">
-        <v>400</v>
       </c>
       <c r="J59" s="3">
         <v>400</v>
@@ -3688,8 +3825,8 @@
       <c r="K59" s="3">
         <v>400</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
+      <c r="L59" s="3">
+        <v>400</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
@@ -3703,14 +3840,14 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3">
-        <v>100</v>
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R59" s="3">
-        <v>0</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="S59" s="3">
+        <v>0</v>
       </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
@@ -3724,28 +3861,31 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E60" s="3">
         <v>700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1500</v>
-      </c>
-      <c r="I60" s="3">
-        <v>1400</v>
       </c>
       <c r="J60" s="3">
         <v>1400</v>
@@ -3754,10 +3894,10 @@
         <v>1400</v>
       </c>
       <c r="L60" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M60" s="3">
         <v>1200</v>
-      </c>
-      <c r="M60" s="3">
-        <v>200</v>
       </c>
       <c r="N60" s="3">
         <v>200</v>
@@ -3769,16 +3909,16 @@
         <v>200</v>
       </c>
       <c r="Q60" s="3">
+        <v>200</v>
+      </c>
+      <c r="R60" s="3">
         <v>300</v>
       </c>
-      <c r="R60" s="3">
-        <v>100</v>
-      </c>
       <c r="S60" s="3">
         <v>100</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
+      <c r="T60" s="3">
+        <v>100</v>
       </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
@@ -3789,17 +3929,20 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>300</v>
+      </c>
+      <c r="E61" s="3">
         <v>200</v>
       </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
@@ -3822,7 +3965,7 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N61" s="3">
         <v>100</v>
@@ -3834,7 +3977,7 @@
         <v>100</v>
       </c>
       <c r="Q61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R61" s="3">
         <v>0</v>
@@ -3854,8 +3997,11 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3898,11 +4044,11 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3">
-        <v>100</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3">
+        <v>100</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
@@ -3919,8 +4065,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3984,8 +4133,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4049,8 +4201,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4114,28 +4269,31 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E66" s="3">
         <v>1000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1500</v>
-      </c>
-      <c r="I66" s="3">
-        <v>1400</v>
       </c>
       <c r="J66" s="3">
         <v>1400</v>
@@ -4144,31 +4302,31 @@
         <v>1400</v>
       </c>
       <c r="L66" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M66" s="3">
         <v>1300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>200</v>
-      </c>
-      <c r="O66" s="3">
-        <v>300</v>
       </c>
       <c r="P66" s="3">
         <v>300</v>
       </c>
       <c r="Q66" s="3">
+        <v>300</v>
+      </c>
+      <c r="R66" s="3">
         <v>400</v>
       </c>
-      <c r="R66" s="3">
-        <v>100</v>
-      </c>
       <c r="S66" s="3">
         <v>100</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
+      <c r="T66" s="3">
+        <v>100</v>
       </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
@@ -4179,8 +4337,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4204,8 +4365,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4269,8 +4431,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4334,8 +4499,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4399,8 +4567,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4464,62 +4635,65 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-45400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-44100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-40600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-37900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-31600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-25900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-20000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-18000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-16000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-13600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-11200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-8700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-6900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-2000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-400</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4529,8 +4703,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4594,8 +4771,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4659,8 +4839,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4724,62 +4907,65 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E76" s="3">
         <v>13500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>15200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>15700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>19200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-1000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-100</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4789,8 +4975,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4854,67 +5043,70 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4924,62 +5116,65 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-7600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-5400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2000</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-2400</v>
       </c>
       <c r="L81" s="3">
         <v>-2400</v>
       </c>
       <c r="M81" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="N81" s="3">
         <v>-2600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-300</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4989,8 +5184,11 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5014,8 +5212,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5049,8 +5248,8 @@
       <c r="M83" s="3">
         <v>0</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
+      <c r="N83" s="3">
+        <v>0</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
@@ -5079,8 +5278,11 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5144,8 +5346,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5209,8 +5414,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5274,8 +5482,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5339,8 +5550,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5404,62 +5618,65 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1000</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-1700</v>
       </c>
       <c r="N89" s="3">
         <v>-1700</v>
       </c>
       <c r="O89" s="3">
-        <v>-1800</v>
+        <v>-1700</v>
       </c>
       <c r="P89" s="3">
         <v>-1800</v>
       </c>
       <c r="Q89" s="3">
-        <v>-600</v>
+        <v>-1800</v>
       </c>
       <c r="R89" s="3">
         <v>-600</v>
       </c>
       <c r="S89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="T89" s="3">
         <v>-100</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5469,8 +5686,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5494,8 +5714,9 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5526,8 +5747,8 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -5559,8 +5780,11 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5624,8 +5848,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5689,8 +5916,11 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5709,20 +5939,20 @@
       <c r="H94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J94" s="3">
         <v>0</v>
       </c>
       <c r="K94" s="3">
-        <v>100</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
+        <v>100</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -5736,8 +5966,8 @@
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
@@ -5754,8 +5984,11 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5779,8 +6012,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5823,8 +6057,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -5844,8 +6078,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5909,8 +6146,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5974,8 +6214,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6039,61 +6282,64 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E100" s="3">
+      <c r="D100" s="3">
+        <v>300</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3">
         <v>2100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1200</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>5000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1500</v>
       </c>
-      <c r="S100" s="3">
-        <v>100</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
+      <c r="T100" s="3">
+        <v>100</v>
       </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
@@ -6104,8 +6350,11 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6124,8 +6373,8 @@
       <c r="H101" s="3">
         <v>0</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
+      <c r="I101" s="3">
+        <v>0</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
@@ -6154,8 +6403,8 @@
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
@@ -6169,23 +6418,26 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>400</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
         <v>0</v>
       </c>
@@ -6193,37 +6445,37 @@
         <v>0</v>
       </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>900</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
+      <c r="T102" s="3">
+        <v>0</v>
       </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
@@ -6232,6 +6484,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
